--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_lastcheck.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_lastcheck.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -47,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,31 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -179,7 +149,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -795,16 +780,16 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -816,52 +801,52 @@
       <c r="J4" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="O4" s="9" t="n">
+      <c r="O4" s="8" t="n">
         <v>97.5</v>
       </c>
-      <c r="P4" s="9" t="n">
+      <c r="P4" s="8" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="S4" s="9" t="n">
+      <c r="S4" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="T4" s="8" t="n">
         <v>56.1</v>
       </c>
-      <c r="U4" s="9" t="n">
+      <c r="U4" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="X4" s="9" t="n">
+      <c r="X4" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="Y4" s="9" t="n">
+      <c r="Y4" s="8" t="n">
         <v>74.3</v>
       </c>
-      <c r="Z4" s="9" t="n">
+      <c r="Z4" s="8" t="n">
         <v>10</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -880,16 +865,16 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -901,52 +886,52 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="8" t="n">
         <v>1.9</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q5" s="9" t="n">
+      <c r="M5" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q5" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R5" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="S5" s="9" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="T5" s="9" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="U5" s="9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V5" s="9" t="n">
+      <c r="R5" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V5" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="X5" s="9" t="n">
+      <c r="X5" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="Y5" s="8" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="Z5" s="9" t="n">
+      <c r="Z5" s="8" t="n">
         <v>1.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -963,18 +948,18 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2368</v>
-      </c>
-      <c r="D6" s="9" t="n">
+        <v>368</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -986,52 +971,52 @@
       <c r="J6" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="N6" s="9" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="O6" s="9" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="P6" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q6" s="9" t="n">
+      <c r="N6" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="S6" s="9" t="n">
+      <c r="S6" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="T6" s="9" t="n">
+      <c r="T6" s="8" t="n">
         <v>59.6</v>
       </c>
-      <c r="U6" s="9" t="n">
+      <c r="U6" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="X6" s="9" t="n">
+      <c r="X6" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="Y6" s="9" t="n">
+      <c r="Y6" s="8" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="Z6" s="9" t="n">
+      <c r="Z6" s="8" t="n">
         <v>9.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1048,18 +1033,18 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>418.2</v>
-      </c>
-      <c r="D7" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D7" s="8" t="n">
         <v>32.4</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1071,52 +1056,52 @@
       <c r="J7" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L7" s="9" t="n">
+      <c r="K7" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L7" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="N7" s="9" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="O7" s="9" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="P7" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q7" s="9" t="n">
+      <c r="N7" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q7" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="S7" s="9" t="n">
+      <c r="S7" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="T7" s="9" t="n">
+      <c r="T7" s="8" t="n">
         <v>59.5</v>
       </c>
-      <c r="U7" s="9" t="n">
+      <c r="U7" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="X7" s="9" t="n">
+      <c r="X7" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="Y7" s="9" t="n">
+      <c r="Y7" s="8" t="n">
         <v>73.2</v>
       </c>
-      <c r="Z7" s="9" t="n">
+      <c r="Z7" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1133,18 +1118,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2368</v>
-      </c>
-      <c r="D8" s="9" t="n">
+        <v>368</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F8" s="9" t="n">
+      <c r="E8" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F8" s="8" t="n">
         <v>27.5</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1156,53 +1141,53 @@
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="N8" s="9" t="n">
+      <c r="N8" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="O8" s="9" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="P8" s="9" t="n">
+      <c r="O8" s="8" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="P8" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="S8" s="9" t="n">
+      <c r="S8" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="T8" s="9" t="n">
+      <c r="T8" s="8" t="n">
         <v>54.8</v>
       </c>
-      <c r="U8" s="9" t="n">
+      <c r="U8" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="W8" s="9" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X8" s="9" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="Y8" s="9" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="Z8" s="9" t="n">
-        <v>7.5</v>
+      <c r="W8" s="8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X8" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="Y8" s="8" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="Z8" s="8" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1220,16 +1205,16 @@
       <c r="C9" s="3" t="n">
         <v>1783.6</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>161.7</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>107.4</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>134.5</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>54.3</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1241,13 +1226,13 @@
       <c r="J9" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K9" s="16" t="n">
+      <c r="K9" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="8" t="n">
         <v>109.4</v>
       </c>
-      <c r="M9" s="16" t="n">
+      <c r="M9" s="8" t="n">
         <v>108</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1259,10 +1244,10 @@
       <c r="P9" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="8" t="n">
         <v>155.6</v>
       </c>
-      <c r="R9" s="16" t="n">
+      <c r="R9" s="9" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1274,20 +1259,20 @@
       <c r="U9" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>135.7</v>
       </c>
-      <c r="W9" s="16" t="n">
+      <c r="W9" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="X9" s="9" t="n">
-        <v>2087.1</v>
-      </c>
-      <c r="Y9" s="9" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="Z9" s="9" t="n">
-        <v>1320</v>
+      <c r="X9" s="3" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>389.1</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>41.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1305,20 +1290,20 @@
       <c r="C10" s="3" t="n">
         <v>356.7</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.4</v>
@@ -1329,49 +1314,49 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="M10" s="16" t="n">
+      <c r="M10" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q10" s="9" t="n">
+      <c r="N10" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q10" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="16" t="n">
+      <c r="R10" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="S10" s="9" t="n">
+      <c r="S10" s="8" t="n">
         <v>31.5</v>
       </c>
-      <c r="T10" s="9" t="n">
+      <c r="T10" s="8" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="U10" s="9" t="n">
+      <c r="U10" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="16" t="n">
+      <c r="W10" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="X10" s="9" t="n">
+      <c r="X10" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="Y10" s="9" t="n">
+      <c r="Y10" s="8" t="n">
         <v>83.2</v>
       </c>
-      <c r="Z10" s="9" t="n">
+      <c r="Z10" s="8" t="n">
         <v>6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1390,73 +1375,73 @@
       <c r="C11" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F11" s="9" t="n">
+      <c r="E11" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="H11" s="18" t="n">
-        <v>88.7</v>
+      <c r="H11" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="M11" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="N11" s="9" t="n">
+      <c r="N11" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="O11" s="9" t="n">
+      <c r="O11" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P11" s="9" t="n">
+      <c r="P11" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>33.2</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="S11" s="9" t="n">
+      <c r="S11" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="T11" s="9" t="n">
+      <c r="T11" s="8" t="n">
         <v>56.3</v>
       </c>
-      <c r="U11" s="9" t="n">
+      <c r="U11" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="X11" s="9" t="n">
+      <c r="X11" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="Y11" s="9" t="n">
+      <c r="Y11" s="8" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="Z11" s="9" t="n">
+      <c r="Z11" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1473,75 +1458,75 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2418.2</v>
-      </c>
-      <c r="D12" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D12" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L12" s="9" t="n">
+      <c r="L12" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="N12" s="9" t="n">
+      <c r="N12" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="O12" s="9" t="n">
+      <c r="O12" s="8" t="n">
         <v>97</v>
       </c>
-      <c r="P12" s="9" t="n">
+      <c r="P12" s="8" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="Q12" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="R12" s="9" t="n">
+      <c r="R12" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="S12" s="9" t="n">
+      <c r="S12" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="T12" s="9" t="n">
+      <c r="T12" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="U12" s="9" t="n">
+      <c r="U12" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" s="8" t="n">
         <v>29.6</v>
       </c>
-      <c r="W12" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X12" s="18" t="n">
+      <c r="W12" s="8" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X12" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="Y12" s="3" t="n">
-        <v>173.2</v>
-      </c>
-      <c r="Z12" s="3" t="n">
+      <c r="Y12" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="Z12" s="8" t="n">
         <v>11.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -1560,74 +1545,74 @@
       <c r="C13" s="3" t="n">
         <v>230.1</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M13" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="N13" s="9" t="n">
+      <c r="N13" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="O13" s="9" t="n">
+      <c r="O13" s="8" t="n">
         <v>98.2</v>
       </c>
-      <c r="P13" s="9" t="n">
+      <c r="P13" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="S13" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="T13" s="9" t="n">
+      <c r="T13" s="8" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="U13" s="9" t="n">
+      <c r="U13" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X13" s="3" t="n">
+      <c r="W13" s="8" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X13" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="Y13" s="3" t="n">
+      <c r="Y13" s="8" t="n">
         <v>80.8</v>
       </c>
-      <c r="Z13" s="3" t="n">
-        <v>16.6</v>
+      <c r="Z13" s="8" t="n">
+        <v>6.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1645,74 +1630,74 @@
       <c r="C14" s="3" t="n">
         <v>121.4</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>27.6</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="K14" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="M14" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="N14" s="9" t="n">
+      <c r="N14" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="O14" s="9" t="n">
+      <c r="O14" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="P14" s="9" t="n">
+      <c r="P14" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="S14" s="9" t="n">
+      <c r="S14" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="T14" s="9" t="n">
+      <c r="T14" s="8" t="n">
         <v>77.8</v>
       </c>
-      <c r="U14" s="9" t="n">
+      <c r="U14" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W14" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X14" s="3" t="n">
+      <c r="W14" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X14" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="Y14" s="3" t="n">
-        <v>185.1</v>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v>15</v>
+      <c r="Y14" s="8" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="Z14" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1728,18 +1713,18 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2340.8</v>
-      </c>
-      <c r="D15" s="9" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="D15" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="8" t="n">
         <v>12.1</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1749,54 +1734,54 @@
         <v>2.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="N15" s="9" t="n">
+      <c r="N15" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="O15" s="9" t="n">
+      <c r="O15" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P15" s="9" t="n">
+      <c r="P15" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="S15" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="T15" s="9" t="n">
+      <c r="T15" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="U15" s="9" t="n">
+      <c r="U15" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="X15" s="9" t="n">
+      <c r="X15" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="Y15" s="9" t="n">
+      <c r="Y15" s="8" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="Z15" s="9" t="n">
+      <c r="Z15" s="8" t="n">
         <v>7.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -1815,20 +1800,20 @@
       <c r="C16" s="3" t="n">
         <v>1530.8</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>154.2</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="G16" s="9" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1192.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.6</v>
@@ -1836,43 +1821,43 @@
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="L16" s="9" t="n">
+      <c r="L16" s="8" t="n">
         <v>102.9</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" s="8" t="n">
         <v>101.9</v>
       </c>
-      <c r="N16" s="9" t="n">
-        <v>1122.4</v>
-      </c>
-      <c r="O16" s="9" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="P16" s="9" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="Q16" s="9" t="n">
+      <c r="N16" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>490</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" s="8" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="16" t="n">
+      <c r="R16" s="9" t="n">
         <v>125.7</v>
       </c>
-      <c r="S16" s="9" t="n">
-        <v>2505.6</v>
-      </c>
-      <c r="T16" s="9" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="U16" s="9" t="n">
-        <v>2993</v>
-      </c>
-      <c r="V16" s="9" t="n">
+      <c r="S16" s="3" t="n">
+        <v>142.7</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>331</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="V16" s="8" t="n">
         <v>136.5</v>
       </c>
-      <c r="W16" s="16" t="n">
+      <c r="W16" s="9" t="n">
         <v>120.4</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1882,7 +1867,7 @@
         <v>386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>142.3</v>
+        <v>42.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1898,18 +1883,18 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>230.6</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="D17" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1922,52 +1907,52 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="N17" s="9" t="n">
+      <c r="N17" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="O17" s="9" t="n">
+      <c r="O17" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="P17" s="9" t="n">
+      <c r="P17" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R17" s="16" t="n">
+      <c r="R17" s="9" t="n">
         <v>25.1</v>
       </c>
-      <c r="S17" s="9" t="n">
+      <c r="S17" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="T17" s="9" t="n">
+      <c r="T17" s="8" t="n">
         <v>72.90000000000001</v>
       </c>
-      <c r="U17" s="9" t="n">
+      <c r="U17" s="8" t="n">
         <v>11.8</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="16" t="n">
+      <c r="W17" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="X17" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>8.5</v>
+      <c r="X17" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y17" s="8" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="Z17" s="8" t="n">
+        <v>6.3</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1983,18 +1968,18 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="D18" s="9" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D18" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="8" t="n">
         <v>13</v>
       </c>
       <c r="H18" s="3" t="n">
@@ -2006,53 +1991,53 @@
       <c r="J18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="M18" s="9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="N18" s="18" t="n">
+      <c r="M18" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N18" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="O18" s="3" t="n">
+      <c r="O18" s="8" t="n">
         <v>97</v>
       </c>
-      <c r="P18" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q18" s="9" t="n">
+      <c r="P18" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="S18" s="9" t="n">
+      <c r="S18" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="T18" s="9" t="n">
+      <c r="T18" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="U18" s="9" t="n">
+      <c r="U18" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="W18" s="9" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="X18" s="9" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="Y18" s="9" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="Z18" s="9" t="n">
-        <v>6.6</v>
+      <c r="W18" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="X18" s="8" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="Y18" s="8" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="Z18" s="8" t="n">
+        <v>8.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2068,18 +2053,18 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="D19" s="9" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="8" t="n">
         <v>11.7</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2091,52 +2076,52 @@
       <c r="J19" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="8" t="n">
         <v>4.2</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="M19" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="N19" s="9" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="O19" s="9" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="P19" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q19" s="9" t="n">
+      <c r="N19" s="8" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P19" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q19" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="S19" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="T19" s="9" t="n">
+      <c r="T19" s="8" t="n">
         <v>60.5</v>
       </c>
-      <c r="U19" s="9" t="n">
+      <c r="U19" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="X19" s="9" t="n">
+      <c r="X19" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="Y19" s="9" t="n">
+      <c r="Y19" s="8" t="n">
         <v>88.5</v>
       </c>
-      <c r="Z19" s="9" t="n">
+      <c r="Z19" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -2155,73 +2140,73 @@
       <c r="C20" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="H20" s="18" t="n">
-        <v>118.4</v>
+      <c r="H20" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="K20" s="8" t="n">
         <v>2.2</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M20" s="9" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N20" s="9" t="n">
+      <c r="M20" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="N20" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="O20" s="9" t="n">
+      <c r="O20" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P20" s="9" t="n">
+      <c r="P20" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q20" s="9" t="n">
+      <c r="Q20" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="R20" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="S20" s="9" t="n">
+      <c r="S20" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="T20" s="9" t="n">
+      <c r="T20" s="8" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="U20" s="9" t="n">
+      <c r="U20" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="V20" s="9" t="n">
+      <c r="V20" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="X20" s="9" t="n">
+      <c r="X20" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="Y20" s="9" t="n">
+      <c r="Y20" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="Z20" s="9" t="n">
+      <c r="Z20" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -2238,21 +2223,21 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="D21" s="9" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="D21" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="18" t="n">
+      <c r="H21" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="I21" s="3" t="n">
@@ -2261,53 +2246,53 @@
       <c r="J21" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K21" s="9" t="n">
+      <c r="K21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M21" s="9" t="n">
+      <c r="M21" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="N21" s="9" t="n">
+      <c r="N21" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="O21" s="9" t="n">
+      <c r="O21" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P21" s="9" t="n">
+      <c r="P21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="S21" s="9" t="n">
+      <c r="S21" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="T21" s="9" t="n">
+      <c r="T21" s="8" t="n">
         <v>63.1</v>
       </c>
-      <c r="U21" s="9" t="n">
+      <c r="U21" s="8" t="n">
         <v>15.7</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="9" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X21" s="9" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="Y21" s="9" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="Z21" s="9" t="n">
-        <v>4</v>
+      <c r="W21" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="Y21" s="8" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="Z21" s="8" t="n">
+        <v>5.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2325,74 +2310,74 @@
       <c r="C22" s="3" t="n">
         <v>294.9</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>25</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>167.4</v>
+        <v>12.9</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="K22" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="N22" s="9" t="n">
+      <c r="N22" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="O22" s="9" t="n">
+      <c r="O22" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P22" s="9" t="n">
+      <c r="P22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R22" s="9" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S22" s="9" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="T22" s="9" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="U22" s="9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="V22" s="9" t="n">
+      <c r="R22" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="W22" s="9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X22" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="Y22" s="9" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="Z22" s="9" t="n">
-        <v>2.4</v>
+      <c r="S22" s="8" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="X22" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="Y22" s="8" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="Z22" s="8" t="n">
+        <v>3.3</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2410,16 +2395,16 @@
       <c r="C23" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="8" t="n">
         <v>155.4</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>96.2</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="8" t="n">
         <v>125.8</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2431,53 +2416,53 @@
       <c r="J23" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="L23" s="9" t="n">
+      <c r="L23" s="8" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="M23" s="9" t="n">
-        <v>98</v>
+      <c r="M23" s="8" t="n">
+        <v>97.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>113.3</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>494</v>
+        <v>94</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q23" s="9" t="n">
+      <c r="Q23" s="8" t="n">
         <v>152.9</v>
       </c>
-      <c r="R23" s="16" t="n">
+      <c r="R23" s="9" t="n">
         <v>124.6</v>
       </c>
-      <c r="S23" s="9" t="n">
-        <v>2419.8</v>
-      </c>
-      <c r="T23" s="9" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="U23" s="9" t="n">
-        <v>3154.6</v>
-      </c>
-      <c r="V23" s="9" t="n">
+      <c r="S23" s="3" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="V23" s="8" t="n">
         <v>129.3</v>
       </c>
-      <c r="W23" s="16" t="n">
+      <c r="W23" s="9" t="n">
         <v>118.9</v>
       </c>
-      <c r="X23" s="9" t="n">
-        <v>2013.5</v>
-      </c>
-      <c r="Y23" s="9" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="Z23" s="9" t="n">
-        <v>790.6</v>
+      <c r="X23" s="3" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="Y23" s="3" t="n">
+        <v>422</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>26.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2495,16 +2480,16 @@
       <c r="C24" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>11.9</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2517,52 +2502,52 @@
         <v>3.7</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="M24" s="9" t="n">
+      <c r="M24" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="N24" s="9" t="n">
+      <c r="N24" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="O24" s="9" t="n">
+      <c r="O24" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="P24" s="9" t="n">
+      <c r="P24" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R24" s="16" t="n">
+      <c r="R24" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="S24" s="9" t="n">
+      <c r="S24" s="8" t="n">
         <v>31.5</v>
       </c>
-      <c r="T24" s="9" t="n">
+      <c r="T24" s="8" t="n">
         <v>71.7</v>
       </c>
-      <c r="U24" s="9" t="n">
+      <c r="U24" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="16" t="n">
+      <c r="W24" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>5.3</v>
+      <c r="X24" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Y24" s="8" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="Z24" s="8" t="n">
+        <v>3.9</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2580,37 +2565,37 @@
       <c r="C25" s="3" t="n">
         <v>177.8</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="K25" s="9" t="n">
+      <c r="K25" s="8" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" s="19" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="M25" s="3" t="n">
+      <c r="L25" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="M25" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N25" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
@@ -2619,34 +2604,34 @@
       <c r="P25" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="S25" s="9" t="n">
+      <c r="S25" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="T25" s="9" t="n">
+      <c r="T25" s="8" t="n">
         <v>95.3</v>
       </c>
-      <c r="U25" s="9" t="n">
+      <c r="U25" s="8" t="n">
         <v>1.3</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="X25" s="9" t="n">
+      <c r="X25" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="Y25" s="9" t="n">
+      <c r="Y25" s="8" t="n">
         <v>97</v>
       </c>
-      <c r="Z25" s="9" t="n">
+      <c r="Z25" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -2663,21 +2648,21 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2345</v>
-      </c>
-      <c r="D26" s="9" t="n">
+        <v>345</v>
+      </c>
+      <c r="D26" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="H26" s="18" t="n">
+      <c r="H26" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2686,52 +2671,52 @@
       <c r="J26" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="N26" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="O26" s="3" t="n">
+      <c r="O26" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="P26" s="3" t="n">
+      <c r="P26" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="S26" s="9" t="n">
+      <c r="S26" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="T26" s="9" t="n">
+      <c r="T26" s="8" t="n">
         <v>55.2</v>
       </c>
-      <c r="U26" s="9" t="n">
+      <c r="U26" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="W26" s="9" t="n">
+      <c r="W26" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="X26" s="9" t="n">
+      <c r="X26" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="Y26" s="9" t="n">
+      <c r="Y26" s="8" t="n">
         <v>74.3</v>
       </c>
-      <c r="Z26" s="9" t="n">
+      <c r="Z26" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -2748,76 +2733,76 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>418.2</v>
-      </c>
-      <c r="D27" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D27" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F27" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="G27" s="9" t="n">
+      <c r="F27" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G27" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="H27" s="18" t="n">
+      <c r="H27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K27" s="9" t="n">
+      <c r="K27" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="9" t="n">
+      <c r="N27" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="O27" s="9" t="n">
+      <c r="O27" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P27" s="9" t="n">
+      <c r="P27" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="S27" s="9" t="n">
+      <c r="S27" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="T27" s="9" t="n">
+      <c r="T27" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="U27" s="9" t="n">
+      <c r="U27" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X27" s="9" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="Y27" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z27" s="9" t="n">
-        <v>8.1</v>
+      <c r="W27" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="Y27" s="8" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="Z27" s="8" t="n">
+        <v>10.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2833,18 +2818,18 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>282.4</v>
-      </c>
-      <c r="D28" s="9" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D28" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2856,53 +2841,53 @@
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="18" t="n">
+      <c r="L28" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M28" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="N28" s="3" t="n">
+      <c r="M28" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="N28" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="O28" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P28" s="3" t="n">
+      <c r="O28" s="8" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P28" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="S28" s="9" t="n">
+      <c r="S28" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="T28" s="9" t="n">
+      <c r="T28" s="8" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="U28" s="9" t="n">
+      <c r="U28" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="W28" s="9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X28" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="Y28" s="9" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="Z28" s="9" t="n">
-        <v>3.1</v>
+      <c r="W28" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="X28" s="8" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="Y28" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z28" s="8" t="n">
+        <v>4.3</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2920,16 +2905,16 @@
       <c r="C29" s="3" t="n">
         <v>146.2</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="8" t="n">
         <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2941,53 +2926,53 @@
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="N29" s="9" t="n">
+      <c r="N29" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="O29" s="8" t="n">
         <v>96.5</v>
       </c>
-      <c r="P29" s="9" t="n">
+      <c r="P29" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="S29" s="9" t="n">
+      <c r="S29" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="T29" s="9" t="n">
+      <c r="T29" s="8" t="n">
         <v>73.7</v>
       </c>
-      <c r="U29" s="9" t="n">
+      <c r="U29" s="8" t="n">
         <v>10.3</v>
       </c>
-      <c r="V29" s="9" t="n">
+      <c r="V29" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W29" s="9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X29" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="Y29" s="9" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="Z29" s="9" t="n">
-        <v>4.3</v>
+      <c r="W29" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="Y29" s="8" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Z29" s="8" t="n">
+        <v>5.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3003,36 +2988,36 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>136.3</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>1363.5</v>
+      </c>
+      <c r="D30" s="8" t="n">
         <v>156.5</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="8" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="F30" s="9" t="n">
-        <v>127.9</v>
-      </c>
-      <c r="G30" s="19" t="n">
-        <v>25.7</v>
+      <c r="F30" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>56.9</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1171.8</v>
-      </c>
-      <c r="K30" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="K30" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="L30" s="16" t="n">
-        <v>102.2</v>
-      </c>
-      <c r="M30" s="16" t="n">
+      <c r="L30" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="M30" s="8" t="n">
         <v>101.1</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3044,35 +3029,35 @@
       <c r="P30" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="8" t="n">
         <v>145.5</v>
       </c>
-      <c r="R30" s="16" t="n">
+      <c r="R30" s="9" t="n">
         <v>121</v>
       </c>
-      <c r="S30" s="9" t="n">
-        <v>2156</v>
-      </c>
-      <c r="T30" s="9" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="U30" s="9" t="n">
-        <v>2378.5</v>
-      </c>
-      <c r="V30" s="9" t="n">
+      <c r="S30" s="3" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="V30" s="8" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="16" t="n">
+      <c r="W30" s="9" t="n">
         <v>115.3</v>
       </c>
-      <c r="X30" s="9" t="n">
-        <v>1787.4</v>
-      </c>
-      <c r="Y30" s="9" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="Z30" s="9" t="n">
-        <v>855.7</v>
+      <c r="X30" s="3" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>30.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3090,16 +3075,16 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3109,55 +3094,55 @@
         <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>13.4</v>
+        <v>3.4</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L31" s="16" t="n">
+      <c r="L31" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M31" s="16" t="n">
+      <c r="M31" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="N31" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="O31" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="P31" s="3" t="n">
+      <c r="O31" s="8" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="P31" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="16" t="n">
+      <c r="R31" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="S31" s="9" t="n">
+      <c r="S31" s="8" t="n">
         <v>30.2</v>
       </c>
-      <c r="T31" s="9" t="n">
+      <c r="T31" s="8" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="U31" s="9" t="n">
+      <c r="U31" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W31" s="16" t="n">
+      <c r="W31" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="X31" s="18" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>6.2</v>
+      <c r="X31" s="8" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="Y31" s="8" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="Z31" s="8" t="n">
+        <v>4.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3175,74 +3160,74 @@
       <c r="C32" s="3" t="n">
         <v>263.5</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="H32" s="18" t="n">
+      <c r="H32" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="K32" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K32" s="8" t="n">
         <v>3.4</v>
       </c>
-      <c r="L32" s="9" t="n">
+      <c r="L32" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="N32" s="9" t="n">
+      <c r="N32" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="O32" s="9" t="n">
+      <c r="O32" s="8" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="P32" s="9" t="n">
+      <c r="P32" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="R32" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="S32" s="9" t="n">
+      <c r="S32" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="T32" s="9" t="n">
+      <c r="T32" s="8" t="n">
         <v>69.8</v>
       </c>
-      <c r="U32" s="9" t="n">
+      <c r="U32" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W32" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X32" s="9" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="Y32" s="9" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="Z32" s="9" t="n">
-        <v>4.4</v>
+      <c r="W32" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="Y32" s="8" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="Z32" s="8" t="n">
+        <v>6.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3260,16 +3245,16 @@
       <c r="C33" s="3" t="n">
         <v>44.1</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="8" t="n">
         <v>4.6</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3281,52 +3266,52 @@
       <c r="J33" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="L33" s="9" t="n">
+      <c r="K33" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L33" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="9" t="n">
+      <c r="N33" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="O33" s="9" t="n">
+      <c r="O33" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="P33" s="9" t="n">
+      <c r="P33" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="R33" s="9" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="T33" s="9" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V33" s="9" t="n">
+      <c r="R33" s="8" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S33" s="8" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="X33" s="9" t="n">
+      <c r="X33" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="Y33" s="9" t="n">
+      <c r="Y33" s="8" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="Z33" s="9" t="n">
+      <c r="Z33" s="8" t="n">
         <v>1.7</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -3345,73 +3330,73 @@
       <c r="C34" s="3" t="n">
         <v>117.2</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="H34" s="18" t="n">
+      <c r="H34" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="8" t="n">
         <v>5.9</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="N34" s="9" t="n">
+      <c r="N34" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="O34" s="9" t="n">
+      <c r="O34" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P34" s="9" t="n">
+      <c r="P34" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="S34" s="9" t="n">
+      <c r="S34" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="T34" s="9" t="n">
+      <c r="T34" s="8" t="n">
         <v>70.2</v>
       </c>
-      <c r="U34" s="9" t="n">
+      <c r="U34" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="V34" s="9" t="n">
+      <c r="V34" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="X34" s="9" t="n">
+      <c r="X34" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="Y34" s="9" t="n">
+      <c r="Y34" s="8" t="n">
         <v>62.5</v>
       </c>
-      <c r="Z34" s="9" t="n">
+      <c r="Z34" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -3430,19 +3415,19 @@
       <c r="C35" s="3" t="n">
         <v>284.4</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="H35" s="18" t="n">
+      <c r="H35" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I35" s="3" t="n">
@@ -3451,53 +3436,53 @@
       <c r="J35" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="8" t="n">
         <v>2.8</v>
       </c>
-      <c r="L35" s="9" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M35" s="9" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N35" s="9" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="O35" s="9" t="n">
+      <c r="L35" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="O35" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P35" s="9" t="n">
+      <c r="P35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="9" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S35" s="9" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="T35" s="9" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="U35" s="9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="V35" s="9" t="n">
+      <c r="R35" s="8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="V35" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W35" s="9" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X35" s="9" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="Y35" s="9" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="Z35" s="9" t="n">
-        <v>3.7</v>
+      <c r="W35" s="8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="Y35" s="8" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="Z35" s="8" t="n">
+        <v>4.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3513,22 +3498,22 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1117.2</v>
-      </c>
-      <c r="D36" s="9" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="D36" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H36" s="18" t="n">
-        <v>119</v>
+      <c r="G36" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.6</v>
@@ -3536,53 +3521,53 @@
       <c r="J36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="8" t="n">
         <v>1.3</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="9" t="n">
+      <c r="N36" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="O36" s="9" t="n">
+      <c r="O36" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="P36" s="9" t="n">
+      <c r="P36" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="S36" s="9" t="n">
+      <c r="S36" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="T36" s="9" t="n">
+      <c r="T36" s="8" t="n">
         <v>94.8</v>
       </c>
-      <c r="U36" s="9" t="n">
+      <c r="U36" s="8" t="n">
         <v>1.3</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W36" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X36" s="9" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="Y36" s="9" t="n">
-        <v>96.40000000000001</v>
-      </c>
-      <c r="Z36" s="9" t="n">
-        <v>0.9</v>
+      <c r="W36" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="X36" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Y36" s="8" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="Z36" s="8" t="n">
+        <v>1.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3600,17 +3585,17 @@
       <c r="C37" s="3" t="n">
         <v>826.4</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="8" t="n">
         <v>142.9</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="8" t="n">
         <v>121.5</v>
       </c>
-      <c r="G37" s="19" t="n">
-        <v>14.3</v>
+      <c r="G37" s="8" t="n">
+        <v>42.9</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
@@ -3621,50 +3606,50 @@
       <c r="J37" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K37" s="16" t="n">
+      <c r="K37" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="L37" s="16" t="n">
+      <c r="L37" s="9" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="16" t="n">
+      <c r="M37" s="9" t="n">
         <v>102.9</v>
       </c>
-      <c r="N37" s="9" t="n">
-        <v>1163.5</v>
-      </c>
-      <c r="O37" s="9" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="P37" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+      <c r="N37" s="3" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>495</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="8" t="n">
         <v>133.1</v>
       </c>
-      <c r="R37" s="16" t="n">
+      <c r="R37" s="9" t="n">
         <v>117.9</v>
       </c>
-      <c r="S37" s="9" t="n">
-        <v>1948.4</v>
-      </c>
-      <c r="T37" s="9" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="U37" s="9" t="n">
-        <v>1202</v>
-      </c>
-      <c r="V37" s="9" t="n">
+      <c r="S37" s="3" t="n">
+        <v>136.3</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>393.6</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="V37" s="8" t="n">
         <v>124.1</v>
       </c>
       <c r="W37" s="9" t="n">
-        <v>110.7</v>
+        <v>112.7</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>129.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>416</v>
+        <v>16</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>28</v>
@@ -3683,21 +3668,21 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="D38" s="9" t="n">
+        <v>165.3</v>
+      </c>
+      <c r="D38" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="H38" s="18" t="n">
+      <c r="H38" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
@@ -3707,52 +3692,52 @@
         <v>1.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L38" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L38" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="16" t="n">
+      <c r="M38" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="N38" s="9" t="n">
+      <c r="N38" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="O38" s="9" t="n">
+      <c r="O38" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P38" s="9" t="n">
+      <c r="P38" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R38" s="16" t="n">
+      <c r="R38" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="S38" s="9" t="n">
+      <c r="S38" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="T38" s="9" t="n">
+      <c r="T38" s="8" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U38" s="9" t="n">
+      <c r="U38" s="8" t="n">
         <v>5.7</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="X38" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y38" s="3" t="n">
-        <v>183.2</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>15.6</v>
+      <c r="X38" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="Y38" s="8" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="Z38" s="8" t="n">
+        <v>4.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3768,75 +3753,75 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.3</v>
-      </c>
-      <c r="D39" s="9" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="9" t="n">
+      <c r="N39" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="O39" s="9" t="n">
+      <c r="O39" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P39" s="9" t="n">
+      <c r="P39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R39" s="9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S39" s="9" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="T39" s="9" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="U39" s="9" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="V39" s="9" t="n">
+      <c r="R39" s="8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V39" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="X39" s="9" t="n">
+      <c r="X39" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="Y39" s="9" t="n">
+      <c r="Y39" s="8" t="n">
         <v>79.3</v>
       </c>
-      <c r="Z39" s="9" t="n">
+      <c r="Z39" s="8" t="n">
         <v>7.7</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -3855,23 +3840,23 @@
       <c r="C40" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E40" s="9" t="n">
-        <v>20.06</v>
-      </c>
-      <c r="F40" s="9" t="n">
+      <c r="E40" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F40" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>3.1</v>
@@ -3879,49 +3864,49 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M40" s="9" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N40" s="9" t="n">
+      <c r="M40" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="N40" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="O40" s="9" t="n">
+      <c r="O40" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P40" s="9" t="n">
+      <c r="P40" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R40" s="9" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S40" s="9" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="T40" s="9" t="n">
-        <v>73</v>
-      </c>
-      <c r="U40" s="9" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V40" s="9" t="n">
+      <c r="R40" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S40" s="8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="V40" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="X40" s="9" t="n">
+      <c r="X40" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="Y40" s="9" t="n">
+      <c r="Y40" s="8" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="Z40" s="9" t="n">
+      <c r="Z40" s="8" t="n">
         <v>8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -3940,72 +3925,72 @@
       <c r="C41" s="3" t="n">
         <v>242.6</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>29.6</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="L41" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L41" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="N41" s="9" t="n">
+      <c r="N41" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="O41" s="9" t="n">
+      <c r="O41" s="8" t="n">
         <v>93.8</v>
       </c>
-      <c r="P41" s="9" t="n">
+      <c r="P41" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R41" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S41" s="9" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="T41" s="9" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="U41" s="9" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="V41" s="9" t="n">
+      <c r="R41" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="V41" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W41" s="9" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X41" s="9" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="Y41" s="9" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="Z41" s="9" t="n">
-        <v>5.1</v>
+      <c r="W41" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="Y41" s="8" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="Z41" s="8" t="n">
+        <v>6.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4023,23 +4008,23 @@
       <c r="C42" s="3" t="n">
         <v>288.6</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>2.9</v>
@@ -4047,50 +4032,50 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="N42" s="9" t="n">
+      <c r="N42" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P42" s="9" t="n">
+      <c r="P42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="S42" s="9" t="n">
+      <c r="S42" s="8" t="n">
         <v>27.6</v>
       </c>
-      <c r="T42" s="9" t="n">
+      <c r="T42" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="U42" s="9" t="n">
+      <c r="U42" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W42" s="9" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X42" s="9" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="Y42" s="9" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="Z42" s="9" t="n">
-        <v>4.9</v>
+      <c r="W42" s="8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="Y42" s="8" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Z42" s="8" t="n">
+        <v>6.5</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4108,23 +4093,23 @@
       <c r="C43" s="3" t="n">
         <v>311.6</v>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="D43" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H43" s="18" t="n">
-        <v>8.6</v>
+      <c r="G43" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>41.6</v>
+        <v>21.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4132,49 +4117,49 @@
       <c r="K43" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="N43" s="9" t="n">
+      <c r="N43" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="O43" s="9" t="n">
+      <c r="O43" s="8" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="P43" s="9" t="n">
+      <c r="P43" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="9" t="n">
+      <c r="R43" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="S43" s="9" t="n">
+      <c r="S43" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="T43" s="9" t="n">
+      <c r="T43" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="U43" s="9" t="n">
+      <c r="U43" s="8" t="n">
         <v>7.1</v>
       </c>
-      <c r="V43" s="9" t="n">
+      <c r="V43" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="W43" s="9" t="n">
+      <c r="W43" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="X43" s="9" t="n">
+      <c r="X43" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="Y43" s="9" t="n">
+      <c r="Y43" s="8" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="Z43" s="9" t="n">
+      <c r="Z43" s="8" t="n">
         <v>3.4</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -4193,26 +4178,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="9" t="inlineStr"/>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="15" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="K44" s="14" t="inlineStr"/>
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="9" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="14" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="9" t="inlineStr"/>
-      <c r="W44" s="9" t="inlineStr"/>
+      <c r="V44" s="8" t="inlineStr"/>
+      <c r="W44" s="14" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4230,19 +4215,19 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1423.4</v>
-      </c>
-      <c r="D45" s="9" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="D45" s="8" t="n">
         <v>152.7</v>
       </c>
-      <c r="E45" s="9" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="F45" s="9" t="n">
+      <c r="E45" s="8" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="F45" s="8" t="n">
         <v>127.4</v>
       </c>
-      <c r="G45" s="19" t="n">
-        <v>19.1</v>
+      <c r="G45" s="8" t="n">
+        <v>50.6</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>93.59999999999999</v>
@@ -4251,16 +4236,16 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="K45" s="16" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K45" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="L45" s="9" t="n">
+      <c r="L45" s="8" t="n">
         <v>103.8</v>
       </c>
-      <c r="M45" s="9" t="n">
-        <v>102.4</v>
+      <c r="M45" s="8" t="n">
+        <v>102.5</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>120.5</v>
@@ -4269,24 +4254,24 @@
         <v>491.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="Q45" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q45" s="8" t="n">
         <v>146.3</v>
       </c>
-      <c r="R45" s="16" t="n">
+      <c r="R45" s="9" t="n">
         <v>122.3</v>
       </c>
-      <c r="S45" s="9" t="n">
-        <v>2248.4</v>
-      </c>
-      <c r="T45" s="9" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="U45" s="9" t="n">
-        <v>2390.2</v>
-      </c>
-      <c r="V45" s="9" t="n">
+      <c r="S45" s="3" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>341.4</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="V45" s="8" t="n">
         <v>134</v>
       </c>
       <c r="W45" s="9" t="n">
@@ -4296,7 +4281,7 @@
         <v>138.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>392.3</v>
+        <v>92.3</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>38</v>
@@ -4317,73 +4302,73 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="18" t="n">
+      <c r="H46" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L46" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="N46" s="9" t="n">
+      <c r="N46" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="O46" s="9" t="n">
+      <c r="O46" s="8" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="P46" s="9" t="n">
+      <c r="P46" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R46" s="16" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="V46" s="9" t="n">
+      <c r="R46" s="9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V46" s="8" t="n">
         <v>26.8</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="X46" s="9" t="n">
+      <c r="X46" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="Y46" s="9" t="n">
+      <c r="Y46" s="8" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="Z46" s="9" t="n">
+      <c r="Z46" s="8" t="n">
         <v>5.8</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_lastcheck.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_lastcheck.xlsx
@@ -143,7 +143,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>18.2</v>
+        <v>418.2</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>32.4</v>
@@ -1247,7 +1247,7 @@
       <c r="Q9" s="8" t="n">
         <v>155.6</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="16" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1262,7 +1262,7 @@
       <c r="V9" s="8" t="n">
         <v>135.7</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="16" t="n">
         <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1303,7 +1303,7 @@
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.4</v>
@@ -1312,7 +1312,7 @@
         <v>4.2</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>21.9</v>
@@ -1332,7 +1332,7 @@
       <c r="Q10" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="16" t="n">
         <v>24.9</v>
       </c>
       <c r="S10" s="8" t="n">
@@ -1347,7 +1347,7 @@
       <c r="V10" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="16" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="8" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>33.3</v>
@@ -1394,7 +1394,7 @@
         <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>18.2</v>
+        <v>418.2</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>32.8</v>
@@ -1803,7 +1803,7 @@
       <c r="D16" s="8" t="n">
         <v>154.2</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="16" t="n">
         <v>99.40000000000001</v>
       </c>
       <c r="F16" s="8" t="n">
@@ -1842,7 +1842,7 @@
       <c r="Q16" s="8" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="9" t="n">
+      <c r="R16" s="16" t="n">
         <v>125.7</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1857,7 +1857,7 @@
       <c r="V16" s="8" t="n">
         <v>136.5</v>
       </c>
-      <c r="W16" s="9" t="n">
+      <c r="W16" s="16" t="n">
         <v>120.4</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1927,7 +1927,7 @@
       <c r="Q17" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="16" t="n">
         <v>25.1</v>
       </c>
       <c r="S17" s="8" t="n">
@@ -1942,7 +1942,7 @@
       <c r="V17" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="16" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="8" t="n">
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332.5</v>
+        <v>332</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>32.2</v>
@@ -2229,7 +2229,7 @@
         <v>30.1</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>24.1</v>
@@ -2319,8 +2319,8 @@
       <c r="F22" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>12.9</v>
+      <c r="G22" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>17.4</v>
@@ -2398,7 +2398,7 @@
       <c r="D23" s="8" t="n">
         <v>155.4</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="16" t="n">
         <v>96.2</v>
       </c>
       <c r="F23" s="8" t="n">
@@ -2429,7 +2429,7 @@
         <v>113.3</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>94</v>
+        <v>494</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>1.3</v>
@@ -2437,7 +2437,7 @@
       <c r="Q23" s="8" t="n">
         <v>152.9</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="16" t="n">
         <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2452,7 +2452,7 @@
       <c r="V23" s="8" t="n">
         <v>129.3</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="16" t="n">
         <v>118.9</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2522,7 +2522,7 @@
       <c r="Q24" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="16" t="n">
         <v>24.9</v>
       </c>
       <c r="S24" s="8" t="n">
@@ -2537,7 +2537,7 @@
       <c r="V24" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="16" t="n">
         <v>23.8</v>
       </c>
       <c r="X24" s="8" t="n">
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>18.2</v>
+        <v>418.2</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>32.9</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>28.2</v>
+        <v>282.4</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>32.6</v>
@@ -3032,7 +3032,7 @@
       <c r="Q30" s="8" t="n">
         <v>145.5</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="16" t="n">
         <v>121</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3047,14 +3047,14 @@
       <c r="V30" s="8" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="9" t="n">
+      <c r="W30" s="16" t="n">
         <v>115.3</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>133.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>11.5</v>
+        <v>411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>30.9</v>
@@ -3097,7 +3097,7 @@
         <v>3.4</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="8" t="n">
         <v>20.4</v>
@@ -3117,7 +3117,7 @@
       <c r="Q31" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="16" t="n">
         <v>24.2</v>
       </c>
       <c r="S31" s="8" t="n">
@@ -3132,7 +3132,7 @@
       <c r="V31" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="16" t="n">
         <v>23.1</v>
       </c>
       <c r="X31" s="8" t="n">
@@ -3440,13 +3440,13 @@
         <v>2.8</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>100</v>
@@ -3609,10 +3609,10 @@
       <c r="K37" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="8" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="8" t="n">
         <v>102.9</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3627,7 +3627,7 @@
       <c r="Q37" s="8" t="n">
         <v>133.1</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="16" t="n">
         <v>117.9</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3642,14 +3642,14 @@
       <c r="V37" s="8" t="n">
         <v>124.1</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="16" t="n">
         <v>112.7</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>129.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>16</v>
+        <v>416</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>28</v>
@@ -3712,7 +3712,7 @@
       <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="16" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="8" t="n">
@@ -3727,7 +3727,7 @@
       <c r="V38" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="16" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="8" t="n">
@@ -3774,7 +3774,7 @@
         <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.8</v>
+        <v>10.1</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>3.5</v>
@@ -3868,7 +3868,7 @@
         <v>21</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N40" s="8" t="n">
         <v>24.6</v>
@@ -4238,14 +4238,14 @@
       <c r="J45" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="16" t="n">
         <v>5</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>103.8</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>102.5</v>
+        <v>102.6</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>120.5</v>
@@ -4259,7 +4259,7 @@
       <c r="Q45" s="8" t="n">
         <v>146.3</v>
       </c>
-      <c r="R45" s="9" t="n">
+      <c r="R45" s="16" t="n">
         <v>122.3</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4274,17 +4274,17 @@
       <c r="V45" s="8" t="n">
         <v>134</v>
       </c>
-      <c r="W45" s="9" t="n">
+      <c r="W45" s="16" t="n">
         <v>119</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>138.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>92.3</v>
+        <v>392.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>20.8</v>
@@ -4344,7 +4344,7 @@
       <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="16" t="n">
         <v>24.5</v>
       </c>
       <c r="S46" s="8" t="n">
@@ -4359,7 +4359,7 @@
       <c r="V46" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W46" s="16" t="n">
         <v>23.8</v>
       </c>
       <c r="X46" s="8" t="n">

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_lastcheck.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_lastcheck.xlsx
@@ -41,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -161,10 +161,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1247,7 +1244,7 @@
       <c r="Q9" s="8" t="n">
         <v>155.6</v>
       </c>
-      <c r="R9" s="16" t="n">
+      <c r="R9" s="15" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1262,7 +1259,7 @@
       <c r="V9" s="8" t="n">
         <v>135.7</v>
       </c>
-      <c r="W9" s="16" t="n">
+      <c r="W9" s="15" t="n">
         <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1332,7 +1329,7 @@
       <c r="Q10" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="16" t="n">
+      <c r="R10" s="15" t="n">
         <v>24.9</v>
       </c>
       <c r="S10" s="8" t="n">
@@ -1347,7 +1344,7 @@
       <c r="V10" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="16" t="n">
+      <c r="W10" s="15" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="8" t="n">
@@ -1373,13 +1370,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>33.3</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>26.6</v>
@@ -1803,13 +1800,13 @@
       <c r="D16" s="8" t="n">
         <v>154.2</v>
       </c>
-      <c r="E16" s="16" t="n">
-        <v>99.40000000000001</v>
+      <c r="E16" s="8" t="n">
+        <v>99.7</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>126.8</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="8" t="n">
         <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1842,7 +1839,7 @@
       <c r="Q16" s="8" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="16" t="n">
+      <c r="R16" s="15" t="n">
         <v>125.7</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1857,7 +1854,7 @@
       <c r="V16" s="8" t="n">
         <v>136.5</v>
       </c>
-      <c r="W16" s="16" t="n">
+      <c r="W16" s="15" t="n">
         <v>120.4</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1927,7 +1924,7 @@
       <c r="Q17" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R17" s="16" t="n">
+      <c r="R17" s="15" t="n">
         <v>25.1</v>
       </c>
       <c r="S17" s="8" t="n">
@@ -1942,7 +1939,7 @@
       <c r="V17" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="16" t="n">
+      <c r="W17" s="15" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="8" t="n">
@@ -1968,7 +1965,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332</v>
+        <v>332.5</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>32.2</v>
@@ -2229,7 +2226,7 @@
         <v>30.1</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>24.1</v>
@@ -2319,8 +2316,8 @@
       <c r="F22" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G22" s="8" t="n">
-        <v>12.4</v>
+      <c r="G22" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>17.4</v>
@@ -2398,7 +2395,7 @@
       <c r="D23" s="8" t="n">
         <v>155.4</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="8" t="n">
         <v>96.2</v>
       </c>
       <c r="F23" s="8" t="n">
@@ -2437,7 +2434,7 @@
       <c r="Q23" s="8" t="n">
         <v>152.9</v>
       </c>
-      <c r="R23" s="16" t="n">
+      <c r="R23" s="15" t="n">
         <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2452,7 +2449,7 @@
       <c r="V23" s="8" t="n">
         <v>129.3</v>
       </c>
-      <c r="W23" s="16" t="n">
+      <c r="W23" s="15" t="n">
         <v>118.9</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2522,7 +2519,7 @@
       <c r="Q24" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R24" s="16" t="n">
+      <c r="R24" s="15" t="n">
         <v>24.9</v>
       </c>
       <c r="S24" s="8" t="n">
@@ -2537,7 +2534,7 @@
       <c r="V24" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="16" t="n">
+      <c r="W24" s="15" t="n">
         <v>23.8</v>
       </c>
       <c r="X24" s="8" t="n">
@@ -2818,7 +2815,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>282.4</v>
+        <v>28.2</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>32.6</v>
@@ -3032,7 +3029,7 @@
       <c r="Q30" s="8" t="n">
         <v>145.5</v>
       </c>
-      <c r="R30" s="16" t="n">
+      <c r="R30" s="15" t="n">
         <v>121</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3047,7 +3044,7 @@
       <c r="V30" s="8" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="16" t="n">
+      <c r="W30" s="15" t="n">
         <v>115.3</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3117,7 +3114,7 @@
       <c r="Q31" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="16" t="n">
+      <c r="R31" s="15" t="n">
         <v>24.2</v>
       </c>
       <c r="S31" s="8" t="n">
@@ -3132,7 +3129,7 @@
       <c r="V31" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W31" s="16" t="n">
+      <c r="W31" s="15" t="n">
         <v>23.1</v>
       </c>
       <c r="X31" s="8" t="n">
@@ -3440,13 +3437,13 @@
         <v>2.8</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>19</v>
+        <v>18.2</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>19</v>
+        <v>18.2</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>21.9</v>
+        <v>20.9</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>100</v>
@@ -3558,16 +3555,16 @@
         <v>21.4</v>
       </c>
       <c r="W36" s="8" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="Y36" s="8" t="n">
-        <v>94.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Z36" s="8" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3609,10 +3606,10 @@
       <c r="K37" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="L37" s="8" t="n">
+      <c r="L37" s="15" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M37" s="15" t="n">
         <v>102.9</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3627,7 +3624,7 @@
       <c r="Q37" s="8" t="n">
         <v>133.1</v>
       </c>
-      <c r="R37" s="16" t="n">
+      <c r="R37" s="15" t="n">
         <v>117.9</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3642,7 +3639,7 @@
       <c r="V37" s="8" t="n">
         <v>124.1</v>
       </c>
-      <c r="W37" s="16" t="n">
+      <c r="W37" s="15" t="n">
         <v>112.7</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3692,7 +3689,7 @@
         <v>1.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="8" t="n">
         <v>20.7</v>
@@ -3712,7 +3709,7 @@
       <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R38" s="16" t="n">
+      <c r="R38" s="15" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="8" t="n">
@@ -3727,7 +3724,7 @@
       <c r="V38" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="W38" s="16" t="n">
+      <c r="W38" s="15" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="8" t="n">
@@ -3774,7 +3771,7 @@
         <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>3.5</v>
@@ -4109,7 +4106,7 @@
         <v>18.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>21.6</v>
+        <v>1.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4176,7 +4173,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="8" t="inlineStr"/>
       <c r="E44" s="8" t="inlineStr"/>
@@ -4215,7 +4212,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1453.4</v>
+        <v>145.3</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>152.7</v>
@@ -4238,7 +4235,7 @@
       <c r="J45" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K45" s="16" t="n">
+      <c r="K45" s="15" t="n">
         <v>5</v>
       </c>
       <c r="L45" s="8" t="n">
@@ -4259,7 +4256,7 @@
       <c r="Q45" s="8" t="n">
         <v>146.3</v>
       </c>
-      <c r="R45" s="16" t="n">
+      <c r="R45" s="15" t="n">
         <v>122.3</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4274,17 +4271,17 @@
       <c r="V45" s="8" t="n">
         <v>134</v>
       </c>
-      <c r="W45" s="16" t="n">
+      <c r="W45" s="15" t="n">
         <v>119</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>138.1</v>
+        <v>13.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>392.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>38.2</v>
+        <v>38.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4324,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>20.8</v>
@@ -4344,7 +4341,7 @@
       <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R46" s="16" t="n">
+      <c r="R46" s="15" t="n">
         <v>24.5</v>
       </c>
       <c r="S46" s="8" t="n">
@@ -4359,7 +4356,7 @@
       <c r="V46" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="W46" s="16" t="n">
+      <c r="W46" s="15" t="n">
         <v>23.8</v>
       </c>
       <c r="X46" s="8" t="n">

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_lastcheck.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_lastcheck.xlsx
@@ -820,7 +820,7 @@
         <v>33</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>23</v>
+        <v>25.6</v>
       </c>
       <c r="S4" s="8" t="n">
         <v>28.1</v>
@@ -835,7 +835,7 @@
         <v>28.6</v>
       </c>
       <c r="W4" s="8" t="n">
-        <v>23.6</v>
+        <v>24.9</v>
       </c>
       <c r="X4" s="8" t="n">
         <v>29.1</v>
@@ -893,19 +893,19 @@
         <v>21.4</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>25.5</v>
+        <v>25.3</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>98.8</v>
+        <v>98.3</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q5" s="8" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>21.9</v>
+        <v>23</v>
       </c>
       <c r="S5" s="8" t="n">
         <v>26.2</v>
@@ -923,13 +923,13 @@
         <v>21.1</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>25</v>
+        <v>24.4</v>
       </c>
       <c r="Y5" s="8" t="n">
-        <v>94.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -978,19 +978,19 @@
         <v>21.3</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>98.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q6" s="8" t="n">
         <v>31.4</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>22.5</v>
+        <v>24.9</v>
       </c>
       <c r="S6" s="8" t="n">
         <v>27.3</v>
@@ -1005,7 +1005,7 @@
         <v>28.3</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="X6" s="8" t="n">
         <v>29</v>
@@ -1063,19 +1063,19 @@
         <v>20.9</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q7" s="8" t="n">
         <v>31.9</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>22.9</v>
+        <v>25.3</v>
       </c>
       <c r="S7" s="8" t="n">
         <v>28</v>
@@ -1090,7 +1090,7 @@
         <v>28.7</v>
       </c>
       <c r="W7" s="8" t="n">
-        <v>23.4</v>
+        <v>24.8</v>
       </c>
       <c r="X7" s="8" t="n">
         <v>28.8</v>
@@ -1160,7 +1160,7 @@
         <v>33.3</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>22.9</v>
+        <v>25.6</v>
       </c>
       <c r="S8" s="8" t="n">
         <v>27.9</v>
@@ -1175,7 +1175,7 @@
         <v>28.1</v>
       </c>
       <c r="W8" s="8" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X8" s="8" t="n">
         <v>28.2</v>
@@ -1244,7 +1244,7 @@
       <c r="Q9" s="8" t="n">
         <v>155.6</v>
       </c>
-      <c r="R9" s="15" t="n">
+      <c r="R9" s="8" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1259,7 +1259,7 @@
       <c r="V9" s="8" t="n">
         <v>135.7</v>
       </c>
-      <c r="W9" s="15" t="n">
+      <c r="W9" s="8" t="n">
         <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1318,43 +1318,43 @@
         <v>21.6</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>98.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q10" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="15" t="n">
+      <c r="R10" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>31.5</v>
+        <v>27.2</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>69.59999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>13.7</v>
+        <v>18</v>
       </c>
       <c r="V10" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="15" t="n">
+      <c r="W10" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>29.8</v>
+        <v>27.7</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>83.2</v>
+        <v>77.2</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>33.2</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>23.2</v>
+        <v>25.8</v>
       </c>
       <c r="S11" s="8" t="n">
         <v>28.5</v>
@@ -1430,7 +1430,7 @@
         <v>29.5</v>
       </c>
       <c r="W11" s="8" t="n">
-        <v>23.5</v>
+        <v>25.1</v>
       </c>
       <c r="X11" s="8" t="n">
         <v>29</v>
@@ -1500,7 +1500,7 @@
         <v>32.8</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>23.4</v>
+        <v>25.8</v>
       </c>
       <c r="S12" s="8" t="n">
         <v>28.7</v>
@@ -1515,7 +1515,7 @@
         <v>29.6</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>24.3</v>
+        <v>25.6</v>
       </c>
       <c r="X12" s="8" t="n">
         <v>30.3</v>
@@ -1573,19 +1573,19 @@
         <v>21</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>98.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q13" s="8" t="n">
         <v>29.1</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="S13" s="8" t="n">
         <v>27.3</v>
@@ -1600,7 +1600,7 @@
         <v>26.4</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>22.8</v>
+        <v>23.8</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>27.8</v>
@@ -1658,19 +1658,19 @@
         <v>20.9</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q14" s="8" t="n">
         <v>27.3</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>23.1</v>
+        <v>24.2</v>
       </c>
       <c r="S14" s="8" t="n">
         <v>28.2</v>
@@ -1685,7 +1685,7 @@
         <v>26</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="X14" s="8" t="n">
         <v>28.6</v>
@@ -1755,7 +1755,7 @@
         <v>30</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>24.1</v>
+        <v>25.6</v>
       </c>
       <c r="S15" s="8" t="n">
         <v>30</v>
@@ -1770,7 +1770,7 @@
         <v>25</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="X15" s="8" t="n">
         <v>24.3</v>
@@ -1839,7 +1839,7 @@
       <c r="Q16" s="8" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="15" t="n">
+      <c r="R16" s="8" t="n">
         <v>125.7</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1854,7 +1854,7 @@
       <c r="V16" s="8" t="n">
         <v>136.5</v>
       </c>
-      <c r="W16" s="15" t="n">
+      <c r="W16" s="8" t="n">
         <v>120.4</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1913,43 +1913,43 @@
         <v>20.4</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q17" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R17" s="15" t="n">
+      <c r="R17" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>31.9</v>
+        <v>28.1</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>11.8</v>
+        <v>15.5</v>
       </c>
       <c r="V17" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="15" t="n">
+      <c r="W17" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="8" t="n">
-        <v>30</v>
+        <v>27.8</v>
       </c>
       <c r="Y17" s="8" t="n">
-        <v>82.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>6.3</v>
+        <v>8.5</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>32.2</v>
       </c>
       <c r="R18" s="8" t="n">
-        <v>22.8</v>
+        <v>25.3</v>
       </c>
       <c r="S18" s="8" t="n">
         <v>27.8</v>
@@ -2025,7 +2025,7 @@
         <v>28.3</v>
       </c>
       <c r="W18" s="8" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="X18" s="8" t="n">
         <v>29.8</v>
@@ -2083,19 +2083,19 @@
         <v>20.7</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q19" s="8" t="n">
         <v>31.7</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>23.1</v>
+        <v>25.3</v>
       </c>
       <c r="S19" s="8" t="n">
         <v>28.2</v>
@@ -2110,7 +2110,7 @@
         <v>25.7</v>
       </c>
       <c r="W19" s="8" t="n">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
       <c r="X19" s="8" t="n">
         <v>29.2</v>
@@ -2180,7 +2180,7 @@
         <v>27.9</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="S20" s="8" t="n">
         <v>26.9</v>
@@ -2195,7 +2195,7 @@
         <v>25</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
       <c r="X20" s="8" t="n">
         <v>26.3</v>
@@ -2265,7 +2265,7 @@
         <v>30.1</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>22.3</v>
+        <v>24.4</v>
       </c>
       <c r="S21" s="8" t="n">
         <v>26.9</v>
@@ -2280,7 +2280,7 @@
         <v>26.3</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="X21" s="8" t="n">
         <v>28.8</v>
@@ -2350,7 +2350,7 @@
         <v>31</v>
       </c>
       <c r="R22" s="8" t="n">
-        <v>24</v>
+        <v>25.8</v>
       </c>
       <c r="S22" s="8" t="n">
         <v>29.9</v>
@@ -2365,7 +2365,7 @@
         <v>24</v>
       </c>
       <c r="W22" s="8" t="n">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="X22" s="8" t="n">
         <v>26.5</v>
@@ -2434,7 +2434,7 @@
       <c r="Q23" s="8" t="n">
         <v>152.9</v>
       </c>
-      <c r="R23" s="15" t="n">
+      <c r="R23" s="8" t="n">
         <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2449,7 +2449,7 @@
       <c r="V23" s="8" t="n">
         <v>129.3</v>
       </c>
-      <c r="W23" s="15" t="n">
+      <c r="W23" s="8" t="n">
         <v>118.9</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2519,32 +2519,32 @@
       <c r="Q24" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R24" s="15" t="n">
+      <c r="R24" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S24" s="8" t="n">
-        <v>31.5</v>
+        <v>27.6</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>71.7</v>
+        <v>62.7</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>12.5</v>
+        <v>16.4</v>
       </c>
       <c r="V24" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="15" t="n">
+      <c r="W24" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>29.5</v>
+        <v>28</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>88.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z24" s="8" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
       <c r="M25" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="N25" s="8" t="n">
+      <c r="N25" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
@@ -2608,13 +2608,13 @@
         <v>22.1</v>
       </c>
       <c r="S25" s="8" t="n">
-        <v>26.6</v>
+        <v>26</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>95.3</v>
+        <v>93.3</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="V25" s="8" t="n">
         <v>21.5</v>
@@ -2623,13 +2623,13 @@
         <v>21</v>
       </c>
       <c r="X25" s="8" t="n">
-        <v>24.9</v>
+        <v>24.5</v>
       </c>
       <c r="Y25" s="8" t="n">
-        <v>97</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="Z25" s="8" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>31.4</v>
       </c>
       <c r="R26" s="8" t="n">
-        <v>21.3</v>
+        <v>24.1</v>
       </c>
       <c r="S26" s="8" t="n">
         <v>25.3</v>
@@ -2705,7 +2705,7 @@
         <v>27.2</v>
       </c>
       <c r="W26" s="8" t="n">
-        <v>22.2</v>
+        <v>23.6</v>
       </c>
       <c r="X26" s="8" t="n">
         <v>26.8</v>
@@ -2775,7 +2775,7 @@
         <v>32.9</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>22</v>
+        <v>24.9</v>
       </c>
       <c r="S27" s="8" t="n">
         <v>26.4</v>
@@ -2790,7 +2790,7 @@
         <v>29.3</v>
       </c>
       <c r="W27" s="8" t="n">
-        <v>24.2</v>
+        <v>25.5</v>
       </c>
       <c r="X27" s="8" t="n">
         <v>30.2</v>
@@ -2860,7 +2860,7 @@
         <v>29.7</v>
       </c>
       <c r="R28" s="8" t="n">
-        <v>23.5</v>
+        <v>25.1</v>
       </c>
       <c r="S28" s="8" t="n">
         <v>28.9</v>
@@ -2875,7 +2875,7 @@
         <v>24.4</v>
       </c>
       <c r="W28" s="8" t="n">
-        <v>21.9</v>
+        <v>22.6</v>
       </c>
       <c r="X28" s="8" t="n">
         <v>26.3</v>
@@ -2945,7 +2945,7 @@
         <v>28.6</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>23.4</v>
+        <v>24.8</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>28.8</v>
@@ -2960,7 +2960,7 @@
         <v>25</v>
       </c>
       <c r="W29" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="X29" s="8" t="n">
         <v>25.9</v>
@@ -3029,7 +3029,7 @@
       <c r="Q30" s="8" t="n">
         <v>145.5</v>
       </c>
-      <c r="R30" s="15" t="n">
+      <c r="R30" s="8" t="n">
         <v>121</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3044,7 +3044,7 @@
       <c r="V30" s="8" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="15" t="n">
+      <c r="W30" s="8" t="n">
         <v>115.3</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3114,32 +3114,32 @@
       <c r="Q31" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="15" t="n">
+      <c r="R31" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>30.2</v>
+        <v>26.8</v>
       </c>
       <c r="T31" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="U31" s="8" t="n">
-        <v>10.1</v>
+        <v>13.5</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W31" s="15" t="n">
+      <c r="W31" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="X31" s="8" t="n">
-        <v>28.3</v>
+        <v>26.6</v>
       </c>
       <c r="Y31" s="8" t="n">
-        <v>86.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="Z31" s="8" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>25.6</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P32" s="8" t="n">
         <v>0.2</v>
@@ -3200,7 +3200,7 @@
         <v>29</v>
       </c>
       <c r="R32" s="8" t="n">
-        <v>22.9</v>
+        <v>24.5</v>
       </c>
       <c r="S32" s="8" t="n">
         <v>27.9</v>
@@ -3215,7 +3215,7 @@
         <v>27.1</v>
       </c>
       <c r="W32" s="8" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="X32" s="8" t="n">
         <v>29.1</v>
@@ -3273,19 +3273,19 @@
         <v>20.6</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="P33" s="8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q33" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="R33" s="8" t="n">
-        <v>21.2</v>
+        <v>22.1</v>
       </c>
       <c r="S33" s="8" t="n">
         <v>25.2</v>
@@ -3303,13 +3303,13 @@
         <v>22</v>
       </c>
       <c r="X33" s="8" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="Y33" s="8" t="n">
-        <v>94.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z33" s="8" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>30.1</v>
       </c>
       <c r="R34" s="8" t="n">
-        <v>24</v>
+        <v>25.6</v>
       </c>
       <c r="S34" s="8" t="n">
         <v>29.9</v>
@@ -3385,7 +3385,7 @@
         <v>26.3</v>
       </c>
       <c r="W34" s="8" t="n">
-        <v>18.6</v>
+        <v>21</v>
       </c>
       <c r="X34" s="8" t="n">
         <v>21.4</v>
@@ -3440,7 +3440,7 @@
         <v>18.2</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>20.9</v>
@@ -3455,7 +3455,7 @@
         <v>28.3</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="S35" s="8" t="n">
         <v>29</v>
@@ -3470,7 +3470,7 @@
         <v>26.3</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
       <c r="X35" s="8" t="n">
         <v>29.3</v>
@@ -3528,19 +3528,19 @@
         <v>21.7</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>98.8</v>
+        <v>98.3</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q36" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="R36" s="8" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="S36" s="8" t="n">
         <v>24.3</v>
@@ -3558,13 +3558,13 @@
         <v>20.8</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>24.6</v>
+        <v>24.1</v>
       </c>
       <c r="Y36" s="8" t="n">
-        <v>96.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="Z36" s="8" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       <c r="L37" s="15" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="15" t="n">
+      <c r="M37" s="8" t="n">
         <v>102.9</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3624,7 +3624,7 @@
       <c r="Q37" s="8" t="n">
         <v>133.1</v>
       </c>
-      <c r="R37" s="15" t="n">
+      <c r="R37" s="8" t="n">
         <v>117.9</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3639,7 +3639,7 @@
       <c r="V37" s="8" t="n">
         <v>124.1</v>
       </c>
-      <c r="W37" s="15" t="n">
+      <c r="W37" s="8" t="n">
         <v>112.7</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3709,32 +3709,32 @@
       <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R38" s="15" t="n">
+      <c r="R38" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="8" t="n">
-        <v>29.1</v>
+        <v>27.1</v>
       </c>
       <c r="T38" s="8" t="n">
-        <v>83.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="U38" s="8" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="V38" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="W38" s="15" t="n">
+      <c r="W38" s="8" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="8" t="n">
-        <v>27.2</v>
+        <v>25.7</v>
       </c>
       <c r="Y38" s="8" t="n">
-        <v>87.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="Z38" s="8" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>19.5</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>22.6</v>
@@ -3795,7 +3795,7 @@
         <v>30.7</v>
       </c>
       <c r="R39" s="8" t="n">
-        <v>23.7</v>
+        <v>25.5</v>
       </c>
       <c r="S39" s="8" t="n">
         <v>29.3</v>
@@ -3813,13 +3813,13 @@
         <v>23.9</v>
       </c>
       <c r="X39" s="8" t="n">
-        <v>29.7</v>
+        <v>27</v>
       </c>
       <c r="Y39" s="8" t="n">
-        <v>79.3</v>
+        <v>72.2</v>
       </c>
       <c r="Z39" s="8" t="n">
-        <v>7.7</v>
+        <v>10.4</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>30.7</v>
       </c>
       <c r="R40" s="8" t="n">
-        <v>23.4</v>
+        <v>25.3</v>
       </c>
       <c r="S40" s="8" t="n">
         <v>28.8</v>
@@ -3898,13 +3898,13 @@
         <v>24</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>29.8</v>
+        <v>27.1</v>
       </c>
       <c r="Y40" s="8" t="n">
-        <v>78.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="Z40" s="8" t="n">
-        <v>8</v>
+        <v>10.7</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>20.9</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>23.2</v>
@@ -3963,7 +3963,7 @@
         <v>29.3</v>
       </c>
       <c r="R41" s="8" t="n">
-        <v>23.4</v>
+        <v>24.9</v>
       </c>
       <c r="S41" s="8" t="n">
         <v>28.7</v>
@@ -3978,7 +3978,7 @@
         <v>27.1</v>
       </c>
       <c r="W41" s="8" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="X41" s="8" t="n">
         <v>29.1</v>
@@ -4048,7 +4048,7 @@
         <v>30.9</v>
       </c>
       <c r="R42" s="8" t="n">
-        <v>22.7</v>
+        <v>24.9</v>
       </c>
       <c r="S42" s="8" t="n">
         <v>27.6</v>
@@ -4063,7 +4063,7 @@
         <v>27.1</v>
       </c>
       <c r="W42" s="8" t="n">
-        <v>23.7</v>
+        <v>24.6</v>
       </c>
       <c r="X42" s="8" t="n">
         <v>29.3</v>
@@ -4121,10 +4121,10 @@
         <v>21.1</v>
       </c>
       <c r="N43" s="8" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="O43" s="8" t="n">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P43" s="8" t="n">
         <v>0.2</v>
@@ -4133,7 +4133,7 @@
         <v>24.7</v>
       </c>
       <c r="R43" s="8" t="n">
-        <v>20.4</v>
+        <v>21.7</v>
       </c>
       <c r="S43" s="8" t="n">
         <v>24</v>
@@ -4151,13 +4151,13 @@
         <v>22</v>
       </c>
       <c r="X43" s="8" t="n">
-        <v>26.4</v>
+        <v>25.1</v>
       </c>
       <c r="Y43" s="8" t="n">
-        <v>88.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="Z43" s="8" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4189,12 +4189,12 @@
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="8" t="inlineStr"/>
-      <c r="R44" s="14" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
       <c r="V44" s="8" t="inlineStr"/>
-      <c r="W44" s="14" t="inlineStr"/>
+      <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4256,7 +4256,7 @@
       <c r="Q45" s="8" t="n">
         <v>146.3</v>
       </c>
-      <c r="R45" s="15" t="n">
+      <c r="R45" s="8" t="n">
         <v>122.3</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4271,7 +4271,7 @@
       <c r="V45" s="8" t="n">
         <v>134</v>
       </c>
-      <c r="W45" s="15" t="n">
+      <c r="W45" s="8" t="n">
         <v>119</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4341,32 +4341,32 @@
       <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R46" s="15" t="n">
+      <c r="R46" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>30.7</v>
+        <v>27.4</v>
       </c>
       <c r="T46" s="8" t="n">
-        <v>75.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="V46" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="W46" s="15" t="n">
+      <c r="W46" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X46" s="8" t="n">
-        <v>29.5</v>
+        <v>27.4</v>
       </c>
       <c r="Y46" s="8" t="n">
-        <v>83.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="Z46" s="8" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
